--- a/DBs/wnba/Results/WNBA_2023_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2023_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerSports\WNBA_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481254D8-B5E7-4741-9C1C-0EEC6BC83111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491635D4-BFF8-4634-87C2-2D9352AC8892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2578" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -179,8 +179,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J521" totalsRowShown="0">
-  <autoFilter ref="A1:J521" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J523" totalsRowShown="0">
+  <autoFilter ref="A1:J523" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9606CA38-2371-480A-B2F8-3A23285B655E}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{B29C85CC-3DBC-401B-A183-ABA3F92B96B9}" name="Season"/>
@@ -514,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FB24B2-7646-4F57-8F9C-DF3DFCDB2AF4}">
-  <dimension ref="A1:J521"/>
+  <dimension ref="A1:J523"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
@@ -12146,16 +12146,16 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
-        <v>45155</v>
+        <v>45153</v>
       </c>
       <c r="B364">
         <v>2023</v>
       </c>
       <c r="C364" t="s">
-        <v>10</v>
-      </c>
-      <c r="D364" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="D364">
+        <v>0.1</v>
       </c>
       <c r="E364" t="s">
         <v>13</v>
@@ -12167,10 +12167,10 @@
         <v>25</v>
       </c>
       <c r="H364">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I364">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J364">
         <v>0</v>
@@ -12178,16 +12178,16 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
-        <v>45155</v>
+        <v>45153</v>
       </c>
       <c r="B365">
         <v>2023</v>
       </c>
       <c r="C365" t="s">
-        <v>10</v>
-      </c>
-      <c r="D365" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="D365">
+        <v>0.1</v>
       </c>
       <c r="E365" t="s">
         <v>24</v>
@@ -12199,10 +12199,10 @@
         <v>26</v>
       </c>
       <c r="H365">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="I365">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J365">
         <v>0</v>
@@ -12210,7 +12210,7 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
-        <v>45156</v>
+        <v>45155</v>
       </c>
       <c r="B366">
         <v>2023</v>
@@ -12222,19 +12222,19 @@
         <v>11</v>
       </c>
       <c r="E366" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F366" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G366" t="s">
         <v>25</v>
       </c>
       <c r="H366">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I366">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J366">
         <v>0</v>
@@ -12242,7 +12242,7 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
-        <v>45156</v>
+        <v>45155</v>
       </c>
       <c r="B367">
         <v>2023</v>
@@ -12254,19 +12254,19 @@
         <v>11</v>
       </c>
       <c r="E367" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F367" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G367" t="s">
         <v>26</v>
       </c>
       <c r="H367">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I367">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J367">
         <v>0</v>
@@ -12286,19 +12286,19 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F368" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G368" t="s">
         <v>25</v>
       </c>
       <c r="H368">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="I368">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J368">
         <v>0</v>
@@ -12318,19 +12318,19 @@
         <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F369" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G369" t="s">
         <v>26</v>
       </c>
       <c r="H369">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I369">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="J369">
         <v>0</v>
@@ -12350,19 +12350,19 @@
         <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F370" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G370" t="s">
         <v>25</v>
       </c>
       <c r="H370">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I370">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J370">
         <v>0</v>
@@ -12382,19 +12382,19 @@
         <v>11</v>
       </c>
       <c r="E371" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F371" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G371" t="s">
         <v>26</v>
       </c>
       <c r="H371">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I371">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J371">
         <v>0</v>
@@ -12414,19 +12414,19 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F372" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G372" t="s">
         <v>25</v>
       </c>
       <c r="H372">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I372">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="J372">
         <v>0</v>
@@ -12446,19 +12446,19 @@
         <v>11</v>
       </c>
       <c r="E373" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F373" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G373" t="s">
         <v>26</v>
       </c>
       <c r="H373">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I373">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J373">
         <v>0</v>
@@ -12478,19 +12478,19 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F374" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G374" t="s">
         <v>25</v>
       </c>
       <c r="H374">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I374">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J374">
         <v>0</v>
@@ -12510,19 +12510,19 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F375" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G375" t="s">
         <v>26</v>
       </c>
       <c r="H375">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I375">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J375">
         <v>0</v>
@@ -12530,7 +12530,7 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
-        <v>45157</v>
+        <v>45156</v>
       </c>
       <c r="B376">
         <v>2023</v>
@@ -12542,10 +12542,10 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F376" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G376" t="s">
         <v>25</v>
@@ -12554,7 +12554,7 @@
         <v>78</v>
       </c>
       <c r="I376">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J376">
         <v>0</v>
@@ -12562,7 +12562,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
-        <v>45157</v>
+        <v>45156</v>
       </c>
       <c r="B377">
         <v>2023</v>
@@ -12574,16 +12574,16 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F377" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G377" t="s">
         <v>26</v>
       </c>
       <c r="H377">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I377">
         <v>78</v>
@@ -12594,7 +12594,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
-        <v>45158</v>
+        <v>45157</v>
       </c>
       <c r="B378">
         <v>2023</v>
@@ -12606,19 +12606,19 @@
         <v>11</v>
       </c>
       <c r="E378" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F378" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G378" t="s">
         <v>25</v>
       </c>
       <c r="H378">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I378">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J378">
         <v>0</v>
@@ -12626,7 +12626,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
-        <v>45158</v>
+        <v>45157</v>
       </c>
       <c r="B379">
         <v>2023</v>
@@ -12638,19 +12638,19 @@
         <v>11</v>
       </c>
       <c r="E379" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F379" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G379" t="s">
         <v>26</v>
       </c>
       <c r="H379">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I379">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J379">
         <v>0</v>
@@ -12670,19 +12670,19 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F380" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G380" t="s">
         <v>25</v>
       </c>
       <c r="H380">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I380">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J380">
         <v>0</v>
@@ -12702,19 +12702,19 @@
         <v>11</v>
       </c>
       <c r="E381" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F381" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G381" t="s">
         <v>26</v>
       </c>
       <c r="H381">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I381">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J381">
         <v>0</v>
@@ -12734,19 +12734,19 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F382" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G382" t="s">
         <v>25</v>
       </c>
       <c r="H382">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I382">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J382">
         <v>0</v>
@@ -12766,19 +12766,19 @@
         <v>11</v>
       </c>
       <c r="E383" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F383" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G383" t="s">
         <v>26</v>
       </c>
       <c r="H383">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I383">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J383">
         <v>0</v>
@@ -12798,19 +12798,19 @@
         <v>11</v>
       </c>
       <c r="E384" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F384" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G384" t="s">
         <v>25</v>
       </c>
       <c r="H384">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="I384">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J384">
         <v>0</v>
@@ -12830,19 +12830,19 @@
         <v>11</v>
       </c>
       <c r="E385" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F385" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G385" t="s">
         <v>26</v>
       </c>
       <c r="H385">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I385">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="J385">
         <v>0</v>
@@ -12850,7 +12850,7 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
-        <v>45160</v>
+        <v>45158</v>
       </c>
       <c r="B386">
         <v>2023</v>
@@ -12862,19 +12862,19 @@
         <v>11</v>
       </c>
       <c r="E386" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F386" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G386" t="s">
         <v>25</v>
       </c>
       <c r="H386">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="I386">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="J386">
         <v>0</v>
@@ -12882,7 +12882,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
-        <v>45160</v>
+        <v>45158</v>
       </c>
       <c r="B387">
         <v>2023</v>
@@ -12894,19 +12894,19 @@
         <v>11</v>
       </c>
       <c r="E387" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F387" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G387" t="s">
         <v>26</v>
       </c>
       <c r="H387">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="I387">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J387">
         <v>0</v>
@@ -12926,19 +12926,19 @@
         <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F388" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G388" t="s">
         <v>25</v>
       </c>
       <c r="H388">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="I388">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J388">
         <v>0</v>
@@ -12958,19 +12958,19 @@
         <v>11</v>
       </c>
       <c r="E389" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F389" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G389" t="s">
         <v>26</v>
       </c>
       <c r="H389">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I389">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="J389">
         <v>0</v>
@@ -12990,19 +12990,19 @@
         <v>11</v>
       </c>
       <c r="E390" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F390" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G390" t="s">
         <v>25</v>
       </c>
       <c r="H390">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I390">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J390">
         <v>0</v>
@@ -13022,19 +13022,19 @@
         <v>11</v>
       </c>
       <c r="E391" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F391" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G391" t="s">
         <v>26</v>
       </c>
       <c r="H391">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="I391">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J391">
         <v>0</v>
@@ -13054,19 +13054,19 @@
         <v>11</v>
       </c>
       <c r="E392" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F392" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G392" t="s">
         <v>25</v>
       </c>
       <c r="H392">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="I392">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="J392">
         <v>0</v>
@@ -13086,19 +13086,19 @@
         <v>11</v>
       </c>
       <c r="E393" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F393" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G393" t="s">
         <v>26</v>
       </c>
       <c r="H393">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="I393">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="J393">
         <v>0</v>
@@ -13106,7 +13106,7 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
-        <v>45161</v>
+        <v>45160</v>
       </c>
       <c r="B394">
         <v>2023</v>
@@ -13118,19 +13118,19 @@
         <v>11</v>
       </c>
       <c r="E394" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F394" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G394" t="s">
         <v>25</v>
       </c>
       <c r="H394">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I394">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="J394">
         <v>0</v>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
-        <v>45161</v>
+        <v>45160</v>
       </c>
       <c r="B395">
         <v>2023</v>
@@ -13150,19 +13150,19 @@
         <v>11</v>
       </c>
       <c r="E395" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F395" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G395" t="s">
         <v>26</v>
       </c>
       <c r="H395">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="I395">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J395">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
-        <v>45162</v>
+        <v>45161</v>
       </c>
       <c r="B396">
         <v>2023</v>
@@ -13182,19 +13182,19 @@
         <v>11</v>
       </c>
       <c r="E396" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F396" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G396" t="s">
         <v>25</v>
       </c>
       <c r="H396">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="I396">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J396">
         <v>0</v>
@@ -13202,7 +13202,7 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
-        <v>45162</v>
+        <v>45161</v>
       </c>
       <c r="B397">
         <v>2023</v>
@@ -13214,19 +13214,19 @@
         <v>11</v>
       </c>
       <c r="E397" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F397" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G397" t="s">
         <v>26</v>
       </c>
       <c r="H397">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I397">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="J397">
         <v>0</v>
@@ -13246,22 +13246,22 @@
         <v>11</v>
       </c>
       <c r="E398" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F398" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G398" t="s">
         <v>25</v>
       </c>
       <c r="H398">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I398">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J398">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.35">
@@ -13278,22 +13278,22 @@
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F399" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G399" t="s">
         <v>26</v>
       </c>
       <c r="H399">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I399">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J399">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.35">
@@ -13310,22 +13310,22 @@
         <v>11</v>
       </c>
       <c r="E400" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F400" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G400" t="s">
         <v>25</v>
       </c>
       <c r="H400">
+        <v>95</v>
+      </c>
+      <c r="I400">
         <v>90</v>
       </c>
-      <c r="I400">
-        <v>81</v>
-      </c>
       <c r="J400">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.35">
@@ -13342,22 +13342,22 @@
         <v>11</v>
       </c>
       <c r="E401" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F401" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G401" t="s">
         <v>26</v>
       </c>
       <c r="H401">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I401">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J401">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.35">
@@ -13374,19 +13374,19 @@
         <v>11</v>
       </c>
       <c r="E402" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F402" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G402" t="s">
         <v>25</v>
       </c>
       <c r="H402">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I402">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J402">
         <v>0</v>
@@ -13406,19 +13406,19 @@
         <v>11</v>
       </c>
       <c r="E403" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F403" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G403" t="s">
         <v>26</v>
       </c>
       <c r="H403">
+        <v>81</v>
+      </c>
+      <c r="I403">
         <v>90</v>
-      </c>
-      <c r="I403">
-        <v>86</v>
       </c>
       <c r="J403">
         <v>0</v>
@@ -13426,7 +13426,7 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
-        <v>45163</v>
+        <v>45162</v>
       </c>
       <c r="B404">
         <v>2023</v>
@@ -13438,19 +13438,19 @@
         <v>11</v>
       </c>
       <c r="E404" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F404" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G404" t="s">
         <v>25</v>
       </c>
       <c r="H404">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I404">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J404">
         <v>0</v>
@@ -13458,7 +13458,7 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
-        <v>45163</v>
+        <v>45162</v>
       </c>
       <c r="B405">
         <v>2023</v>
@@ -13470,19 +13470,19 @@
         <v>11</v>
       </c>
       <c r="E405" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F405" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G405" t="s">
         <v>26</v>
       </c>
       <c r="H405">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I405">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J405">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
-        <v>45164</v>
+        <v>45163</v>
       </c>
       <c r="B406">
         <v>2023</v>
@@ -13502,19 +13502,19 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F406" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G406" t="s">
         <v>25</v>
       </c>
       <c r="H406">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="I406">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J406">
         <v>0</v>
@@ -13522,7 +13522,7 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
-        <v>45164</v>
+        <v>45163</v>
       </c>
       <c r="B407">
         <v>2023</v>
@@ -13534,19 +13534,19 @@
         <v>11</v>
       </c>
       <c r="E407" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F407" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G407" t="s">
         <v>26</v>
       </c>
       <c r="H407">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I407">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="J407">
         <v>0</v>
@@ -13566,19 +13566,19 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F408" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G408" t="s">
         <v>25</v>
       </c>
       <c r="H408">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="I408">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J408">
         <v>0</v>
@@ -13598,19 +13598,19 @@
         <v>11</v>
       </c>
       <c r="E409" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F409" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G409" t="s">
         <v>26</v>
       </c>
       <c r="H409">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I409">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="J409">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
-        <v>45165</v>
+        <v>45164</v>
       </c>
       <c r="B410">
         <v>2023</v>
@@ -13630,19 +13630,19 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F410" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G410" t="s">
         <v>25</v>
       </c>
       <c r="H410">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="I410">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J410">
         <v>0</v>
@@ -13650,7 +13650,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
-        <v>45165</v>
+        <v>45164</v>
       </c>
       <c r="B411">
         <v>2023</v>
@@ -13662,19 +13662,19 @@
         <v>11</v>
       </c>
       <c r="E411" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F411" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G411" t="s">
         <v>26</v>
       </c>
       <c r="H411">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I411">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J411">
         <v>0</v>
@@ -13694,16 +13694,16 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F412" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G412" t="s">
         <v>25</v>
       </c>
       <c r="H412">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I412">
         <v>83</v>
@@ -13726,10 +13726,10 @@
         <v>11</v>
       </c>
       <c r="E413" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F413" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G413" t="s">
         <v>26</v>
@@ -13738,7 +13738,7 @@
         <v>83</v>
       </c>
       <c r="I413">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="J413">
         <v>0</v>
@@ -13758,19 +13758,19 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F414" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G414" t="s">
         <v>25</v>
       </c>
       <c r="H414">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I414">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J414">
         <v>0</v>
@@ -13790,19 +13790,19 @@
         <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F415" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G415" t="s">
         <v>26</v>
       </c>
       <c r="H415">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I415">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J415">
         <v>0</v>
@@ -13822,19 +13822,19 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F416" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G416" t="s">
         <v>25</v>
       </c>
       <c r="H416">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I416">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="J416">
         <v>0</v>
@@ -13854,19 +13854,19 @@
         <v>11</v>
       </c>
       <c r="E417" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F417" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G417" t="s">
         <v>26</v>
       </c>
       <c r="H417">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I417">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J417">
         <v>0</v>
@@ -13874,7 +13874,7 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
-        <v>45166</v>
+        <v>45165</v>
       </c>
       <c r="B418">
         <v>2023</v>
@@ -13886,19 +13886,19 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F418" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G418" t="s">
         <v>25</v>
       </c>
       <c r="H418">
+        <v>90</v>
+      </c>
+      <c r="I418">
         <v>85</v>
-      </c>
-      <c r="I418">
-        <v>94</v>
       </c>
       <c r="J418">
         <v>0</v>
@@ -13906,7 +13906,7 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
-        <v>45166</v>
+        <v>45165</v>
       </c>
       <c r="B419">
         <v>2023</v>
@@ -13918,19 +13918,19 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F419" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G419" t="s">
         <v>26</v>
       </c>
       <c r="H419">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="I419">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J419">
         <v>0</v>
@@ -13938,7 +13938,7 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
-        <v>45167</v>
+        <v>45166</v>
       </c>
       <c r="B420">
         <v>2023</v>
@@ -13950,16 +13950,16 @@
         <v>11</v>
       </c>
       <c r="E420" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F420" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G420" t="s">
         <v>25</v>
       </c>
       <c r="H420">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I420">
         <v>94</v>
@@ -13970,7 +13970,7 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
-        <v>45167</v>
+        <v>45166</v>
       </c>
       <c r="B421">
         <v>2023</v>
@@ -13982,10 +13982,10 @@
         <v>11</v>
       </c>
       <c r="E421" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F421" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G421" t="s">
         <v>26</v>
@@ -13994,7 +13994,7 @@
         <v>94</v>
       </c>
       <c r="I421">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J421">
         <v>0</v>
@@ -14014,10 +14014,10 @@
         <v>11</v>
       </c>
       <c r="E422" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F422" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G422" t="s">
         <v>25</v>
@@ -14026,7 +14026,7 @@
         <v>76</v>
       </c>
       <c r="I422">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="J422">
         <v>0</v>
@@ -14046,16 +14046,16 @@
         <v>11</v>
       </c>
       <c r="E423" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F423" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G423" t="s">
         <v>26</v>
       </c>
       <c r="H423">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="I423">
         <v>76</v>
@@ -14078,19 +14078,19 @@
         <v>11</v>
       </c>
       <c r="E424" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F424" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G424" t="s">
         <v>25</v>
       </c>
       <c r="H424">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I424">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="J424">
         <v>0</v>
@@ -14110,19 +14110,19 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F425" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G425" t="s">
         <v>26</v>
       </c>
       <c r="H425">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I425">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J425">
         <v>0</v>
@@ -14130,7 +14130,7 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
-        <v>45169</v>
+        <v>45167</v>
       </c>
       <c r="B426">
         <v>2023</v>
@@ -14142,19 +14142,19 @@
         <v>11</v>
       </c>
       <c r="E426" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F426" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G426" t="s">
         <v>25</v>
       </c>
       <c r="H426">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I426">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J426">
         <v>0</v>
@@ -14162,7 +14162,7 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
-        <v>45169</v>
+        <v>45167</v>
       </c>
       <c r="B427">
         <v>2023</v>
@@ -14174,19 +14174,19 @@
         <v>11</v>
       </c>
       <c r="E427" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F427" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G427" t="s">
         <v>26</v>
       </c>
       <c r="H427">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I427">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J427">
         <v>0</v>
@@ -14206,19 +14206,19 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F428" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G428" t="s">
         <v>25</v>
       </c>
       <c r="H428">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I428">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="J428">
         <v>0</v>
@@ -14238,19 +14238,19 @@
         <v>11</v>
       </c>
       <c r="E429" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F429" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G429" t="s">
         <v>26</v>
       </c>
       <c r="H429">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="I429">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J429">
         <v>0</v>
@@ -14270,19 +14270,19 @@
         <v>11</v>
       </c>
       <c r="E430" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F430" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G430" t="s">
         <v>25</v>
       </c>
       <c r="H430">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I430">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="J430">
         <v>0</v>
@@ -14302,19 +14302,19 @@
         <v>11</v>
       </c>
       <c r="E431" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F431" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G431" t="s">
         <v>26</v>
       </c>
       <c r="H431">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="I431">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J431">
         <v>0</v>
@@ -14322,7 +14322,7 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
-        <v>45170</v>
+        <v>45169</v>
       </c>
       <c r="B432">
         <v>2023</v>
@@ -14334,19 +14334,19 @@
         <v>11</v>
       </c>
       <c r="E432" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F432" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G432" t="s">
         <v>25</v>
       </c>
       <c r="H432">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="I432">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="J432">
         <v>0</v>
@@ -14354,7 +14354,7 @@
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
-        <v>45170</v>
+        <v>45169</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -14366,19 +14366,19 @@
         <v>11</v>
       </c>
       <c r="E433" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F433" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G433" t="s">
         <v>26</v>
       </c>
       <c r="H433">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="I433">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="J433">
         <v>0</v>
@@ -14398,22 +14398,22 @@
         <v>11</v>
       </c>
       <c r="E434" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F434" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G434" t="s">
         <v>25</v>
       </c>
       <c r="H434">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="I434">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J434">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.35">
@@ -14430,22 +14430,22 @@
         <v>11</v>
       </c>
       <c r="E435" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F435" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G435" t="s">
         <v>26</v>
       </c>
       <c r="H435">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="I435">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="J435">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.35">
@@ -14462,22 +14462,22 @@
         <v>11</v>
       </c>
       <c r="E436" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F436" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G436" t="s">
         <v>25</v>
       </c>
       <c r="H436">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="I436">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J436">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.35">
@@ -14494,27 +14494,27 @@
         <v>11</v>
       </c>
       <c r="E437" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F437" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G437" t="s">
         <v>26</v>
       </c>
       <c r="H437">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I437">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="J437">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
-        <v>45171</v>
+        <v>45170</v>
       </c>
       <c r="B438">
         <v>2023</v>
@@ -14526,19 +14526,19 @@
         <v>11</v>
       </c>
       <c r="E438" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F438" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G438" t="s">
         <v>25</v>
       </c>
       <c r="H438">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I438">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="J438">
         <v>0</v>
@@ -14546,7 +14546,7 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
-        <v>45171</v>
+        <v>45170</v>
       </c>
       <c r="B439">
         <v>2023</v>
@@ -14558,19 +14558,19 @@
         <v>11</v>
       </c>
       <c r="E439" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F439" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G439" t="s">
         <v>26</v>
       </c>
       <c r="H439">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I439">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="J439">
         <v>0</v>
@@ -14578,7 +14578,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
-        <v>45172</v>
+        <v>45171</v>
       </c>
       <c r="B440">
         <v>2023</v>
@@ -14590,19 +14590,19 @@
         <v>11</v>
       </c>
       <c r="E440" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F440" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G440" t="s">
         <v>25</v>
       </c>
       <c r="H440">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I440">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="J440">
         <v>0</v>
@@ -14610,7 +14610,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
-        <v>45172</v>
+        <v>45171</v>
       </c>
       <c r="B441">
         <v>2023</v>
@@ -14622,19 +14622,19 @@
         <v>11</v>
       </c>
       <c r="E441" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F441" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G441" t="s">
         <v>26</v>
       </c>
       <c r="H441">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="I441">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J441">
         <v>0</v>
@@ -14654,22 +14654,22 @@
         <v>11</v>
       </c>
       <c r="E442" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F442" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G442" t="s">
         <v>25</v>
       </c>
       <c r="H442">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I442">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="J442">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.35">
@@ -14686,22 +14686,22 @@
         <v>11</v>
       </c>
       <c r="E443" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F443" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G443" t="s">
         <v>26</v>
       </c>
       <c r="H443">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="I443">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="J443">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.35">
@@ -14718,22 +14718,22 @@
         <v>11</v>
       </c>
       <c r="E444" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F444" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G444" t="s">
         <v>25</v>
       </c>
       <c r="H444">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I444">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="J444">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.35">
@@ -14750,22 +14750,22 @@
         <v>11</v>
       </c>
       <c r="E445" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F445" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G445" t="s">
         <v>26</v>
       </c>
       <c r="H445">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I445">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="J445">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.35">
@@ -14782,19 +14782,19 @@
         <v>11</v>
       </c>
       <c r="E446" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F446" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G446" t="s">
         <v>25</v>
       </c>
       <c r="H446">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I446">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="J446">
         <v>0</v>
@@ -14814,19 +14814,19 @@
         <v>11</v>
       </c>
       <c r="E447" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F447" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G447" t="s">
         <v>26</v>
       </c>
       <c r="H447">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="I447">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J447">
         <v>0</v>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
-        <v>45174</v>
+        <v>45172</v>
       </c>
       <c r="B448">
         <v>2023</v>
@@ -14846,19 +14846,19 @@
         <v>11</v>
       </c>
       <c r="E448" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F448" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G448" t="s">
         <v>25</v>
       </c>
       <c r="H448">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I448">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J448">
         <v>0</v>
@@ -14866,7 +14866,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
-        <v>45174</v>
+        <v>45172</v>
       </c>
       <c r="B449">
         <v>2023</v>
@@ -14878,19 +14878,19 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F449" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G449" t="s">
         <v>26</v>
       </c>
       <c r="H449">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I449">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J449">
         <v>0</v>
@@ -14910,19 +14910,19 @@
         <v>11</v>
       </c>
       <c r="E450" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F450" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G450" t="s">
         <v>25</v>
       </c>
       <c r="H450">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I450">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J450">
         <v>0</v>
@@ -14942,19 +14942,19 @@
         <v>11</v>
       </c>
       <c r="E451" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F451" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G451" t="s">
         <v>26</v>
       </c>
       <c r="H451">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I451">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J451">
         <v>0</v>
@@ -14974,19 +14974,19 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F452" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G452" t="s">
         <v>25</v>
       </c>
       <c r="H452">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I452">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J452">
         <v>0</v>
@@ -15006,19 +15006,19 @@
         <v>11</v>
       </c>
       <c r="E453" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F453" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G453" t="s">
         <v>26</v>
       </c>
       <c r="H453">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I453">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J453">
         <v>0</v>
@@ -15038,19 +15038,19 @@
         <v>11</v>
       </c>
       <c r="E454" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F454" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G454" t="s">
         <v>25</v>
       </c>
       <c r="H454">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I454">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="J454">
         <v>0</v>
@@ -15070,19 +15070,19 @@
         <v>11</v>
       </c>
       <c r="E455" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F455" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G455" t="s">
         <v>26</v>
       </c>
       <c r="H455">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I455">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J455">
         <v>0</v>
@@ -15090,7 +15090,7 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
-        <v>45175</v>
+        <v>45174</v>
       </c>
       <c r="B456">
         <v>2023</v>
@@ -15102,19 +15102,19 @@
         <v>11</v>
       </c>
       <c r="E456" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F456" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G456" t="s">
         <v>25</v>
       </c>
       <c r="H456">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="I456">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J456">
         <v>0</v>
@@ -15122,7 +15122,7 @@
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
-        <v>45175</v>
+        <v>45174</v>
       </c>
       <c r="B457">
         <v>2023</v>
@@ -15134,19 +15134,19 @@
         <v>11</v>
       </c>
       <c r="E457" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F457" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G457" t="s">
         <v>26</v>
       </c>
       <c r="H457">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I457">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="J457">
         <v>0</v>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
-        <v>45176</v>
+        <v>45175</v>
       </c>
       <c r="B458">
         <v>2023</v>
@@ -15166,19 +15166,19 @@
         <v>11</v>
       </c>
       <c r="E458" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F458" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G458" t="s">
         <v>25</v>
       </c>
       <c r="H458">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="I458">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="J458">
         <v>0</v>
@@ -15186,7 +15186,7 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
-        <v>45176</v>
+        <v>45175</v>
       </c>
       <c r="B459">
         <v>2023</v>
@@ -15198,19 +15198,19 @@
         <v>11</v>
       </c>
       <c r="E459" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F459" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G459" t="s">
         <v>26</v>
       </c>
       <c r="H459">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="I459">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="J459">
         <v>0</v>
@@ -15218,7 +15218,7 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
-        <v>45177</v>
+        <v>45176</v>
       </c>
       <c r="B460">
         <v>2023</v>
@@ -15230,19 +15230,19 @@
         <v>11</v>
       </c>
       <c r="E460" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F460" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G460" t="s">
         <v>25</v>
       </c>
       <c r="H460">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I460">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J460">
         <v>0</v>
@@ -15250,7 +15250,7 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
-        <v>45177</v>
+        <v>45176</v>
       </c>
       <c r="B461">
         <v>2023</v>
@@ -15262,19 +15262,19 @@
         <v>11</v>
       </c>
       <c r="E461" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F461" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G461" t="s">
         <v>26</v>
       </c>
       <c r="H461">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I461">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J461">
         <v>0</v>
@@ -15294,19 +15294,19 @@
         <v>11</v>
       </c>
       <c r="E462" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F462" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G462" t="s">
         <v>25</v>
       </c>
       <c r="H462">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="I462">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="J462">
         <v>0</v>
@@ -15326,19 +15326,19 @@
         <v>11</v>
       </c>
       <c r="E463" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F463" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G463" t="s">
         <v>26</v>
       </c>
       <c r="H463">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="I463">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="J463">
         <v>0</v>
@@ -15358,19 +15358,19 @@
         <v>11</v>
       </c>
       <c r="E464" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F464" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G464" t="s">
         <v>25</v>
       </c>
       <c r="H464">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="I464">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="J464">
         <v>0</v>
@@ -15390,19 +15390,19 @@
         <v>11</v>
       </c>
       <c r="E465" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F465" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G465" t="s">
         <v>26</v>
       </c>
       <c r="H465">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="I465">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="J465">
         <v>0</v>
@@ -15422,19 +15422,19 @@
         <v>11</v>
       </c>
       <c r="E466" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F466" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G466" t="s">
         <v>25</v>
       </c>
       <c r="H466">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I466">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="J466">
         <v>0</v>
@@ -15454,19 +15454,19 @@
         <v>11</v>
       </c>
       <c r="E467" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F467" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G467" t="s">
         <v>26</v>
       </c>
       <c r="H467">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="I467">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J467">
         <v>0</v>
@@ -15486,19 +15486,19 @@
         <v>11</v>
       </c>
       <c r="E468" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F468" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G468" t="s">
         <v>25</v>
       </c>
       <c r="H468">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I468">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J468">
         <v>0</v>
@@ -15518,19 +15518,19 @@
         <v>11</v>
       </c>
       <c r="E469" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F469" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G469" t="s">
         <v>26</v>
       </c>
       <c r="H469">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I469">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J469">
         <v>0</v>
@@ -15538,7 +15538,7 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
-        <v>45179</v>
+        <v>45177</v>
       </c>
       <c r="B470">
         <v>2023</v>
@@ -15550,19 +15550,19 @@
         <v>11</v>
       </c>
       <c r="E470" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F470" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G470" t="s">
         <v>25</v>
       </c>
       <c r="H470">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I470">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J470">
         <v>0</v>
@@ -15570,7 +15570,7 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
-        <v>45179</v>
+        <v>45177</v>
       </c>
       <c r="B471">
         <v>2023</v>
@@ -15582,19 +15582,19 @@
         <v>11</v>
       </c>
       <c r="E471" t="s">
+        <v>12</v>
+      </c>
+      <c r="F471" t="s">
         <v>21</v>
       </c>
-      <c r="F471" t="s">
-        <v>22</v>
-      </c>
       <c r="G471" t="s">
         <v>26</v>
       </c>
       <c r="H471">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I471">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J471">
         <v>0</v>
@@ -15614,22 +15614,22 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F472" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G472" t="s">
         <v>25</v>
       </c>
       <c r="H472">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I472">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J472">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.35">
@@ -15646,22 +15646,22 @@
         <v>11</v>
       </c>
       <c r="E473" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F473" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G473" t="s">
         <v>26</v>
       </c>
       <c r="H473">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I473">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="J473">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.35">
@@ -15678,22 +15678,22 @@
         <v>11</v>
       </c>
       <c r="E474" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F474" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G474" t="s">
         <v>25</v>
       </c>
       <c r="H474">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I474">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J474">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.35">
@@ -15710,22 +15710,22 @@
         <v>11</v>
       </c>
       <c r="E475" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F475" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G475" t="s">
         <v>26</v>
       </c>
       <c r="H475">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I475">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="J475">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.35">
@@ -15742,19 +15742,19 @@
         <v>11</v>
       </c>
       <c r="E476" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F476" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G476" t="s">
         <v>25</v>
       </c>
       <c r="H476">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I476">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="J476">
         <v>0</v>
@@ -15774,19 +15774,19 @@
         <v>11</v>
       </c>
       <c r="E477" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F477" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G477" t="s">
         <v>26</v>
       </c>
       <c r="H477">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="I477">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="J477">
         <v>0</v>
@@ -15806,19 +15806,19 @@
         <v>11</v>
       </c>
       <c r="E478" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F478" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G478" t="s">
         <v>25</v>
       </c>
       <c r="H478">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I478">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J478">
         <v>0</v>
@@ -15838,19 +15838,19 @@
         <v>11</v>
       </c>
       <c r="E479" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F479" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G479" t="s">
         <v>26</v>
       </c>
       <c r="H479">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="I479">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J479">
         <v>0</v>
@@ -15870,19 +15870,19 @@
         <v>11</v>
       </c>
       <c r="E480" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F480" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G480" t="s">
         <v>25</v>
       </c>
       <c r="H480">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I480">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J480">
         <v>0</v>
@@ -15902,19 +15902,19 @@
         <v>11</v>
       </c>
       <c r="E481" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F481" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G481" t="s">
         <v>26</v>
       </c>
       <c r="H481">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I481">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J481">
         <v>0</v>
@@ -15922,31 +15922,31 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
-        <v>45182</v>
+        <v>45179</v>
       </c>
       <c r="B482">
         <v>2023</v>
       </c>
       <c r="C482" t="s">
-        <v>23</v>
-      </c>
-      <c r="D482">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D482" t="s">
+        <v>11</v>
       </c>
       <c r="E482" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F482" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G482" t="s">
         <v>25</v>
       </c>
       <c r="H482">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="I482">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J482">
         <v>0</v>
@@ -15954,31 +15954,31 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
-        <v>45182</v>
+        <v>45179</v>
       </c>
       <c r="B483">
         <v>2023</v>
       </c>
       <c r="C483" t="s">
-        <v>23</v>
-      </c>
-      <c r="D483">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D483" t="s">
+        <v>11</v>
       </c>
       <c r="E483" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F483" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G483" t="s">
         <v>26</v>
       </c>
       <c r="H483">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I483">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="J483">
         <v>0</v>
@@ -15998,19 +15998,19 @@
         <v>1</v>
       </c>
       <c r="E484" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F484" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G484" t="s">
         <v>25</v>
       </c>
       <c r="H484">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I484">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J484">
         <v>0</v>
@@ -16030,19 +16030,19 @@
         <v>1</v>
       </c>
       <c r="E485" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F485" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G485" t="s">
         <v>26</v>
       </c>
       <c r="H485">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I485">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J485">
         <v>0</v>
@@ -16050,7 +16050,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
-        <v>45184</v>
+        <v>45182</v>
       </c>
       <c r="B486">
         <v>2023</v>
@@ -16062,19 +16062,19 @@
         <v>1</v>
       </c>
       <c r="E486" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F486" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G486" t="s">
         <v>25</v>
       </c>
       <c r="H486">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="I486">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J486">
         <v>0</v>
@@ -16082,7 +16082,7 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
-        <v>45184</v>
+        <v>45182</v>
       </c>
       <c r="B487">
         <v>2023</v>
@@ -16094,19 +16094,19 @@
         <v>1</v>
       </c>
       <c r="E487" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F487" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G487" t="s">
         <v>26</v>
       </c>
       <c r="H487">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I487">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="J487">
         <v>0</v>
@@ -16126,19 +16126,19 @@
         <v>1</v>
       </c>
       <c r="E488" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F488" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G488" t="s">
         <v>25</v>
       </c>
       <c r="H488">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I488">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J488">
         <v>0</v>
@@ -16158,19 +16158,19 @@
         <v>1</v>
       </c>
       <c r="E489" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F489" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G489" t="s">
         <v>26</v>
       </c>
       <c r="H489">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I489">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J489">
         <v>0</v>
@@ -16178,7 +16178,7 @@
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
-        <v>45186</v>
+        <v>45184</v>
       </c>
       <c r="B490">
         <v>2023</v>
@@ -16190,19 +16190,19 @@
         <v>1</v>
       </c>
       <c r="E490" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F490" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G490" t="s">
         <v>25</v>
       </c>
       <c r="H490">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I490">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J490">
         <v>0</v>
@@ -16210,7 +16210,7 @@
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
-        <v>45186</v>
+        <v>45184</v>
       </c>
       <c r="B491">
         <v>2023</v>
@@ -16222,19 +16222,19 @@
         <v>1</v>
       </c>
       <c r="E491" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F491" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G491" t="s">
         <v>26</v>
       </c>
       <c r="H491">
+        <v>90</v>
+      </c>
+      <c r="I491">
         <v>75</v>
-      </c>
-      <c r="I491">
-        <v>82</v>
       </c>
       <c r="J491">
         <v>0</v>
@@ -16254,19 +16254,19 @@
         <v>1</v>
       </c>
       <c r="E492" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F492" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G492" t="s">
         <v>25</v>
       </c>
       <c r="H492">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I492">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="J492">
         <v>0</v>
@@ -16286,19 +16286,19 @@
         <v>1</v>
       </c>
       <c r="E493" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F493" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G493" t="s">
         <v>26</v>
       </c>
       <c r="H493">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I493">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="J493">
         <v>0</v>
@@ -16306,7 +16306,7 @@
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
-        <v>45188</v>
+        <v>45186</v>
       </c>
       <c r="B494">
         <v>2023</v>
@@ -16318,19 +16318,19 @@
         <v>1</v>
       </c>
       <c r="E494" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F494" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G494" t="s">
         <v>25</v>
       </c>
       <c r="H494">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I494">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="J494">
         <v>0</v>
@@ -16338,7 +16338,7 @@
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
-        <v>45188</v>
+        <v>45186</v>
       </c>
       <c r="B495">
         <v>2023</v>
@@ -16350,19 +16350,19 @@
         <v>1</v>
       </c>
       <c r="E495" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F495" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G495" t="s">
         <v>26</v>
       </c>
       <c r="H495">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I495">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J495">
         <v>0</v>
@@ -16382,22 +16382,22 @@
         <v>1</v>
       </c>
       <c r="E496" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F496" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G496" t="s">
         <v>25</v>
       </c>
       <c r="H496">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I496">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J496">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.35">
@@ -16414,27 +16414,27 @@
         <v>1</v>
       </c>
       <c r="E497" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F497" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G497" t="s">
         <v>26</v>
       </c>
       <c r="H497">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="I497">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="J497">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
-        <v>45189</v>
+        <v>45188</v>
       </c>
       <c r="B498">
         <v>2023</v>
@@ -16446,27 +16446,27 @@
         <v>1</v>
       </c>
       <c r="E498" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F498" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G498" t="s">
         <v>25</v>
       </c>
       <c r="H498">
+        <v>85</v>
+      </c>
+      <c r="I498">
         <v>90</v>
       </c>
-      <c r="I498">
-        <v>75</v>
-      </c>
       <c r="J498">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
-        <v>45189</v>
+        <v>45188</v>
       </c>
       <c r="B499">
         <v>2023</v>
@@ -16478,27 +16478,27 @@
         <v>1</v>
       </c>
       <c r="E499" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F499" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G499" t="s">
         <v>26</v>
       </c>
       <c r="H499">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I499">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J499">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
-        <v>45193</v>
+        <v>45189</v>
       </c>
       <c r="B500">
         <v>2023</v>
@@ -16507,22 +16507,22 @@
         <v>23</v>
       </c>
       <c r="D500">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E500" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F500" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G500" t="s">
         <v>25</v>
       </c>
       <c r="H500">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I500">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="J500">
         <v>0</v>
@@ -16530,7 +16530,7 @@
     </row>
     <row r="501" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
-        <v>45193</v>
+        <v>45189</v>
       </c>
       <c r="B501">
         <v>2023</v>
@@ -16539,22 +16539,22 @@
         <v>23</v>
       </c>
       <c r="D501">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E501" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F501" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G501" t="s">
         <v>26</v>
       </c>
       <c r="H501">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="I501">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J501">
         <v>0</v>
@@ -16574,19 +16574,19 @@
         <v>2</v>
       </c>
       <c r="E502" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F502" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G502" t="s">
         <v>25</v>
       </c>
       <c r="H502">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I502">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="J502">
         <v>0</v>
@@ -16606,19 +16606,19 @@
         <v>2</v>
       </c>
       <c r="E503" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F503" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G503" t="s">
         <v>26</v>
       </c>
       <c r="H503">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="I503">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J503">
         <v>0</v>
@@ -16626,7 +16626,7 @@
     </row>
     <row r="504" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
-        <v>45195</v>
+        <v>45193</v>
       </c>
       <c r="B504">
         <v>2023</v>
@@ -16638,19 +16638,19 @@
         <v>2</v>
       </c>
       <c r="E504" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F504" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G504" t="s">
         <v>25</v>
       </c>
       <c r="H504">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I504">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="J504">
         <v>0</v>
@@ -16658,7 +16658,7 @@
     </row>
     <row r="505" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
-        <v>45195</v>
+        <v>45193</v>
       </c>
       <c r="B505">
         <v>2023</v>
@@ -16670,19 +16670,19 @@
         <v>2</v>
       </c>
       <c r="E505" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F505" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G505" t="s">
         <v>26</v>
       </c>
       <c r="H505">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="I505">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="J505">
         <v>0</v>
@@ -16702,19 +16702,19 @@
         <v>2</v>
       </c>
       <c r="E506" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F506" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G506" t="s">
         <v>25</v>
       </c>
       <c r="H506">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I506">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J506">
         <v>0</v>
@@ -16734,19 +16734,19 @@
         <v>2</v>
       </c>
       <c r="E507" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F507" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G507" t="s">
         <v>26</v>
       </c>
       <c r="H507">
+        <v>91</v>
+      </c>
+      <c r="I507">
         <v>84</v>
-      </c>
-      <c r="I507">
-        <v>77</v>
       </c>
       <c r="J507">
         <v>0</v>
@@ -16754,7 +16754,7 @@
     </row>
     <row r="508" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
-        <v>45198</v>
+        <v>45195</v>
       </c>
       <c r="B508">
         <v>2023</v>
@@ -16766,19 +16766,19 @@
         <v>2</v>
       </c>
       <c r="E508" t="s">
+        <v>19</v>
+      </c>
+      <c r="F508" t="s">
         <v>13</v>
       </c>
-      <c r="F508" t="s">
-        <v>19</v>
-      </c>
       <c r="G508" t="s">
         <v>25</v>
       </c>
       <c r="H508">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I508">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J508">
         <v>0</v>
@@ -16786,7 +16786,7 @@
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
-        <v>45198</v>
+        <v>45195</v>
       </c>
       <c r="B509">
         <v>2023</v>
@@ -16798,19 +16798,19 @@
         <v>2</v>
       </c>
       <c r="E509" t="s">
+        <v>13</v>
+      </c>
+      <c r="F509" t="s">
         <v>19</v>
       </c>
-      <c r="F509" t="s">
-        <v>13</v>
-      </c>
       <c r="G509" t="s">
         <v>26</v>
       </c>
       <c r="H509">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I509">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="J509">
         <v>0</v>
@@ -16830,19 +16830,19 @@
         <v>2</v>
       </c>
       <c r="E510" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F510" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G510" t="s">
         <v>25</v>
       </c>
       <c r="H510">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="I510">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J510">
         <v>0</v>
@@ -16862,19 +16862,19 @@
         <v>2</v>
       </c>
       <c r="E511" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F511" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G511" t="s">
         <v>26</v>
       </c>
       <c r="H511">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I511">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="J511">
         <v>0</v>
@@ -16882,7 +16882,7 @@
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
-        <v>45200</v>
+        <v>45198</v>
       </c>
       <c r="B512">
         <v>2023</v>
@@ -16894,19 +16894,19 @@
         <v>2</v>
       </c>
       <c r="E512" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F512" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G512" t="s">
         <v>25</v>
       </c>
       <c r="H512">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="I512">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="J512">
         <v>0</v>
@@ -16914,7 +16914,7 @@
     </row>
     <row r="513" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
-        <v>45200</v>
+        <v>45198</v>
       </c>
       <c r="B513">
         <v>2023</v>
@@ -16926,19 +16926,19 @@
         <v>2</v>
       </c>
       <c r="E513" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F513" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G513" t="s">
         <v>26</v>
       </c>
       <c r="H513">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="I513">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="J513">
         <v>0</v>
@@ -16946,7 +16946,7 @@
     </row>
     <row r="514" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
-        <v>45207</v>
+        <v>45200</v>
       </c>
       <c r="B514">
         <v>2023</v>
@@ -16955,22 +16955,22 @@
         <v>23</v>
       </c>
       <c r="D514">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E514" t="s">
         <v>13</v>
       </c>
       <c r="F514" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G514" t="s">
         <v>25</v>
       </c>
       <c r="H514">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I514">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="J514">
         <v>0</v>
@@ -16978,7 +16978,7 @@
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
-        <v>45207</v>
+        <v>45200</v>
       </c>
       <c r="B515">
         <v>2023</v>
@@ -16987,10 +16987,10 @@
         <v>23</v>
       </c>
       <c r="D515">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E515" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F515" t="s">
         <v>13</v>
@@ -16999,10 +16999,10 @@
         <v>26</v>
       </c>
       <c r="H515">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="I515">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J515">
         <v>0</v>
@@ -17010,7 +17010,7 @@
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
-        <v>45210</v>
+        <v>45207</v>
       </c>
       <c r="B516">
         <v>2023</v>
@@ -17031,10 +17031,10 @@
         <v>25</v>
       </c>
       <c r="H516">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I516">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J516">
         <v>0</v>
@@ -17042,7 +17042,7 @@
     </row>
     <row r="517" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
-        <v>45210</v>
+        <v>45207</v>
       </c>
       <c r="B517">
         <v>2023</v>
@@ -17063,10 +17063,10 @@
         <v>26</v>
       </c>
       <c r="H517">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I517">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J517">
         <v>0</v>
@@ -17074,7 +17074,7 @@
     </row>
     <row r="518" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
-        <v>45214</v>
+        <v>45210</v>
       </c>
       <c r="B518">
         <v>2023</v>
@@ -17086,19 +17086,19 @@
         <v>3</v>
       </c>
       <c r="E518" t="s">
+        <v>13</v>
+      </c>
+      <c r="F518" t="s">
         <v>24</v>
       </c>
-      <c r="F518" t="s">
-        <v>13</v>
-      </c>
       <c r="G518" t="s">
         <v>25</v>
       </c>
       <c r="H518">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I518">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="J518">
         <v>0</v>
@@ -17106,7 +17106,7 @@
     </row>
     <row r="519" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
-        <v>45214</v>
+        <v>45210</v>
       </c>
       <c r="B519">
         <v>2023</v>
@@ -17118,19 +17118,19 @@
         <v>3</v>
       </c>
       <c r="E519" t="s">
+        <v>24</v>
+      </c>
+      <c r="F519" t="s">
         <v>13</v>
       </c>
-      <c r="F519" t="s">
-        <v>24</v>
-      </c>
       <c r="G519" t="s">
         <v>26</v>
       </c>
       <c r="H519">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="I519">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J519">
         <v>0</v>
@@ -17138,7 +17138,7 @@
     </row>
     <row r="520" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
-        <v>45217</v>
+        <v>45214</v>
       </c>
       <c r="B520">
         <v>2023</v>
@@ -17159,10 +17159,10 @@
         <v>25</v>
       </c>
       <c r="H520">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I520">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="J520">
         <v>0</v>
@@ -17170,7 +17170,7 @@
     </row>
     <row r="521" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
-        <v>45217</v>
+        <v>45214</v>
       </c>
       <c r="B521">
         <v>2023</v>
@@ -17191,12 +17191,76 @@
         <v>26</v>
       </c>
       <c r="H521">
+        <v>87</v>
+      </c>
+      <c r="I521">
+        <v>73</v>
+      </c>
+      <c r="J521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A522" s="1">
+        <v>45217</v>
+      </c>
+      <c r="B522">
+        <v>2023</v>
+      </c>
+      <c r="C522" t="s">
+        <v>23</v>
+      </c>
+      <c r="D522">
+        <v>3</v>
+      </c>
+      <c r="E522" t="s">
+        <v>24</v>
+      </c>
+      <c r="F522" t="s">
+        <v>13</v>
+      </c>
+      <c r="G522" t="s">
+        <v>25</v>
+      </c>
+      <c r="H522">
+        <v>70</v>
+      </c>
+      <c r="I522">
         <v>69</v>
       </c>
-      <c r="I521">
+      <c r="J522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A523" s="1">
+        <v>45217</v>
+      </c>
+      <c r="B523">
+        <v>2023</v>
+      </c>
+      <c r="C523" t="s">
+        <v>23</v>
+      </c>
+      <c r="D523">
+        <v>3</v>
+      </c>
+      <c r="E523" t="s">
+        <v>13</v>
+      </c>
+      <c r="F523" t="s">
+        <v>24</v>
+      </c>
+      <c r="G523" t="s">
+        <v>26</v>
+      </c>
+      <c r="H523">
+        <v>69</v>
+      </c>
+      <c r="I523">
         <v>70</v>
       </c>
-      <c r="J521">
+      <c r="J523">
         <v>0</v>
       </c>
     </row>
